--- a/experiments/03_dataset_comparison/report/dev_v1_original_vs_dev_v1_dictionary_gpt_comparison.xlsx
+++ b/experiments/03_dataset_comparison/report/dev_v1_original_vs_dev_v1_dictionary_gpt_comparison.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,6 +27,9 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <color rgb="00006100"/>
     </font>
   </fonts>
   <fills count="4">
@@ -106,7 +109,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -114,7 +117,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>

--- a/experiments/03_dataset_comparison/report/dev_v1_original_vs_dev_v1_dictionary_gpt_comparison.xlsx
+++ b/experiments/03_dataset_comparison/report/dev_v1_original_vs_dev_v1_dictionary_gpt_comparison.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,10 +29,13 @@
       <b val="1"/>
     </font>
     <font>
+      <color rgb="009C6500"/>
+    </font>
+    <font>
       <color rgb="00006100"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +46,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
         <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -98,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -118,6 +127,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -640,7 +655,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
@@ -651,7 +666,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
@@ -691,7 +706,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
@@ -702,7 +717,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
@@ -742,7 +757,7 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="F5" s="7" t="n">
@@ -753,7 +768,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="I5" s="7" t="n">
@@ -795,7 +810,7 @@
       <c r="D6" s="3" t="n">
         <v>54.12488479371674</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>dev_v1_dictionary</t>
         </is>
@@ -806,7 +821,7 @@
       <c r="G6" s="3" t="n">
         <v>78.36526438321229</v>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>dev_v1_dictionary</t>
         </is>
@@ -817,7 +832,7 @@
       <c r="J6" s="3" t="n">
         <v>70.56000000000002</v>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>dev_v1_dictionary</t>
         </is>
@@ -828,7 +843,7 @@
       <c r="M6" s="3" t="n">
         <v>0.9288117048923646</v>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>dev_v1_dictionary</t>
         </is>
@@ -839,7 +854,7 @@
       <c r="P6" s="3" t="n">
         <v>0.8423390081421178</v>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="Q6" s="9" t="inlineStr">
         <is>
           <t>dev_v1_dictionary</t>
         </is>
@@ -858,7 +873,7 @@
       <c r="D7" s="3" t="n">
         <v>43.49889848461612</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>dev_v1_dictionary</t>
         </is>
@@ -869,7 +884,7 @@
       <c r="G7" s="3" t="n">
         <v>72.45995024990887</v>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>dev_v1_dictionary</t>
         </is>
@@ -880,7 +895,7 @@
       <c r="J7" s="3" t="n">
         <v>73.90393294648615</v>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>dev_v1_dictionary</t>
         </is>
@@ -891,7 +906,7 @@
       <c r="M7" s="3" t="n">
         <v>0.929763008632753</v>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="9" t="inlineStr">
         <is>
           <t>dev_v1_dictionary</t>
         </is>
@@ -902,7 +917,7 @@
       <c r="P7" s="3" t="n">
         <v>0.774401473296503</v>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="Q7" s="9" t="inlineStr">
         <is>
           <t>dev_v1_dictionary</t>
         </is>
@@ -921,7 +936,7 @@
       <c r="D8" s="7" t="n">
         <v>64.83165350095547</v>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>dev_v1_dictionary</t>
         </is>
@@ -932,7 +947,7 @@
       <c r="G8" s="7" t="n">
         <v>82.25934468449383</v>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>dev_v1_dictionary</t>
         </is>
@@ -943,7 +958,7 @@
       <c r="J8" s="7" t="n">
         <v>92.94871794871796</v>
       </c>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="K8" s="10" t="inlineStr">
         <is>
           <t>dev_v1_dictionary</t>
         </is>
@@ -954,7 +969,7 @@
       <c r="M8" s="7" t="n">
         <v>0.9527865808420228</v>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>dev_v1_dictionary</t>
         </is>
@@ -965,7 +980,7 @@
       <c r="P8" s="7" t="n">
         <v>0.8671814671814662</v>
       </c>
-      <c r="Q8" s="8" t="inlineStr">
+      <c r="Q8" s="10" t="inlineStr">
         <is>
           <t>dev_v1_dictionary</t>
         </is>
@@ -990,7 +1005,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
@@ -1001,7 +1016,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
@@ -1012,7 +1027,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="L9" s="3" t="n">
@@ -1023,7 +1038,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="O9" s="3" t="n">
@@ -1034,7 +1049,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1068,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
@@ -1064,7 +1079,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
@@ -1075,7 +1090,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="L10" s="3" t="n">
@@ -1086,7 +1101,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="O10" s="3" t="n">
@@ -1097,7 +1112,7 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1131,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="F11" s="7" t="n">
@@ -1127,7 +1142,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="I11" s="7" t="n">
@@ -1138,7 +1153,7 @@
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="L11" s="7" t="n">
@@ -1149,7 +1164,7 @@
       </c>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="O11" s="7" t="n">
@@ -1160,7 +1175,7 @@
       </c>
       <c r="Q11" s="8" t="inlineStr">
         <is>
-          <t>dev_v1_dictionary</t>
+          <t>tie</t>
         </is>
       </c>
     </row>
